--- a/backtest_runs/20260410_193731/by_symbol/LOTCHEM/LOTCHEM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/LOTCHEM/LOTCHEM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-3706.599999999998</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>96293.40000000001</v>
@@ -633,7 +633,7 @@
         <v>-2327.399999999996</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>98189.79999999999</v>
@@ -679,7 +679,7 @@
         <v>-7671.799999999989</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>90518</v>
@@ -817,7 +817,7 @@
         <v>-215.5000000000031</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>107197.7</v>
@@ -863,7 +863,7 @@
         <v>-1077.5</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>106120.2</v>
@@ -955,7 +955,7 @@
         <v>-172.3999999999963</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>107068.4</v>
@@ -1093,7 +1093,7 @@
         <v>-818.8999999999902</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>109223.4</v>
@@ -1185,7 +1185,7 @@
         <v>-2155</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>111162.9</v>
@@ -1277,7 +1277,7 @@
         <v>-1551.599999999998</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>112283.5</v>
@@ -1323,7 +1323,7 @@
         <v>-646.4999999999939</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>111637</v>
@@ -1415,7 +1415,7 @@
         <v>-2284.300000000005</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>112973.1</v>
@@ -1461,7 +1461,7 @@
         <v>-1206.799999999989</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>111766.3</v>
@@ -1553,7 +1553,7 @@
         <v>-1379.200000000001</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>111335.3</v>
@@ -1645,7 +1645,7 @@
         <v>-5128.900000000005</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>113792</v>
